--- a/sites/DEMO001/photos.xlsx
+++ b/sites/DEMO001/photos.xlsx
@@ -212,161 +212,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2857500" cy="1466850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2857500" cy="1466850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2857500" cy="1466850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2857500" cy="1466850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2857500" cy="1466850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2857500" cy="1466850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -749,11 +594,7 @@
           <t>J1 GL</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>※サンプル写真（実データではありません）</t>
-        </is>
-      </c>
+      <c r="C6" s="8" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
     </row>
@@ -838,6 +679,5 @@
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>